--- a/artfynd/A 28474-2023 artfynd.xlsx
+++ b/artfynd/A 28474-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136011276</v>
       </c>
       <c r="B2" t="n">
-        <v>58451</v>
+        <v>58453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28474-2023 artfynd.xlsx
+++ b/artfynd/A 28474-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136011276</v>
       </c>
       <c r="B2" t="n">
-        <v>58453</v>
+        <v>58454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28474-2023 artfynd.xlsx
+++ b/artfynd/A 28474-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136011276</v>
       </c>
       <c r="B2" t="n">
-        <v>58454</v>
+        <v>58458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28474-2023 artfynd.xlsx
+++ b/artfynd/A 28474-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136011276</v>
       </c>
       <c r="B2" t="n">
-        <v>58458</v>
+        <v>58459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28474-2023 artfynd.xlsx
+++ b/artfynd/A 28474-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136011276</v>
       </c>
       <c r="B2" t="n">
-        <v>58459</v>
+        <v>58464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28474-2023 artfynd.xlsx
+++ b/artfynd/A 28474-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136011276</v>
       </c>
       <c r="B2" t="n">
-        <v>58464</v>
+        <v>58477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
